--- a/data/example_of_old_method.xlsx
+++ b/data/example_of_old_method.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/henaolab/Documents/R/bactcountr_shiny/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2095D7-B3A6-EE40-B174-83211432D7A4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0D8F12-EF94-0E45-9220-80A0242C5781}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2420" yWindow="980" windowWidth="14540" windowHeight="26580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -514,6 +514,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -583,6 +587,21 @@
       <c r="D3" t="s">
         <v>8</v>
       </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E66" si="0">D3*(5^C3)*10*0.5</f>
+        <v>825</v>
+      </c>
+      <c r="F3">
+        <v>0.5</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G66" si="1">E3/F3</f>
+        <v>1650</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H66" si="2">LOG(G3)</f>
+        <v>3.2174839442139063</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
@@ -597,6 +616,21 @@
       <c r="D4" t="s">
         <v>10</v>
       </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>625</v>
+      </c>
+      <c r="F4">
+        <v>0.5</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="1"/>
+        <v>1250</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="2"/>
+        <v>3.0969100130080562</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
@@ -611,6 +645,21 @@
       <c r="D5" t="s">
         <v>5</v>
       </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0.5</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H5" t="e">
+        <f t="shared" si="2"/>
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6">
@@ -625,6 +674,21 @@
       <c r="D6" t="s">
         <v>13</v>
       </c>
+      <c r="E6" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F6">
+        <v>0.5</v>
+      </c>
+      <c r="G6" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H6" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7">
@@ -639,6 +703,21 @@
       <c r="D7" t="s">
         <v>13</v>
       </c>
+      <c r="E7" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F7">
+        <v>0.5</v>
+      </c>
+      <c r="G7" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H7" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
@@ -653,6 +732,21 @@
       <c r="D8" t="s">
         <v>14</v>
       </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>7250</v>
+      </c>
+      <c r="F8">
+        <v>0.5</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>14500</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="2"/>
+        <v>4.1613680022349753</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
@@ -667,6 +761,21 @@
       <c r="D9" t="s">
         <v>15</v>
       </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>3750</v>
+      </c>
+      <c r="F9">
+        <v>0.5</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>7500</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="2"/>
+        <v>3.8750612633917001</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
@@ -681,6 +790,21 @@
       <c r="D10" t="s">
         <v>13</v>
       </c>
+      <c r="E10" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F10">
+        <v>0.5</v>
+      </c>
+      <c r="G10" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H10" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
@@ -695,6 +819,21 @@
       <c r="D11" t="s">
         <v>17</v>
       </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="F11">
+        <v>0.5</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="1"/>
+        <v>4050</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="2"/>
+        <v>3.6074550232146687</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
@@ -709,6 +848,21 @@
       <c r="D12" t="s">
         <v>18</v>
       </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>875</v>
+      </c>
+      <c r="F12">
+        <v>0.5</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="1"/>
+        <v>1750</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="2"/>
+        <v>3.2430380486862944</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13">
@@ -723,6 +877,21 @@
       <c r="D13" t="s">
         <v>9</v>
       </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="F13">
+        <v>0.5</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="2"/>
+        <v>3.3979400086720375</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14">
@@ -737,6 +906,21 @@
       <c r="D14" t="s">
         <v>13</v>
       </c>
+      <c r="E14" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F14">
+        <v>0.5</v>
+      </c>
+      <c r="G14" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H14" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15">
@@ -751,6 +935,21 @@
       <c r="D15" t="s">
         <v>9</v>
       </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="F15">
+        <v>0.5</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
@@ -765,8 +964,23 @@
       <c r="D16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0.5</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H16" t="e">
+        <f t="shared" si="2"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2</v>
       </c>
@@ -779,8 +993,23 @@
       <c r="D17" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>625</v>
+      </c>
+      <c r="F17">
+        <v>0.5</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="1"/>
+        <v>1250</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="2"/>
+        <v>3.0969100130080562</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
@@ -793,8 +1022,23 @@
       <c r="D18" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="F18">
+        <v>0.5</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="1"/>
+        <v>140</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="2"/>
+        <v>2.1461280356782382</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>2</v>
       </c>
@@ -807,8 +1051,23 @@
       <c r="D19" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0.5</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H19" t="e">
+        <f t="shared" si="2"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2</v>
       </c>
@@ -821,8 +1080,23 @@
       <c r="D20" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0.5</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H20" t="e">
+        <f t="shared" si="2"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>2</v>
       </c>
@@ -835,8 +1109,23 @@
       <c r="D21" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0.5</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H21" t="e">
+        <f t="shared" si="2"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>2</v>
       </c>
@@ -849,8 +1138,23 @@
       <c r="D22" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E22" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F22">
+        <v>0.5</v>
+      </c>
+      <c r="G22" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H22" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>2</v>
       </c>
@@ -863,8 +1167,23 @@
       <c r="D23" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="F23">
+        <v>0.5</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="1"/>
+        <v>1600</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="2"/>
+        <v>3.2041199826559246</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2</v>
       </c>
@@ -877,8 +1196,23 @@
       <c r="D24" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24">
+        <f t="shared" si="0"/>
+        <v>875</v>
+      </c>
+      <c r="F24">
+        <v>0.5</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="1"/>
+        <v>1750</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="2"/>
+        <v>3.2430380486862944</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2</v>
       </c>
@@ -891,8 +1225,23 @@
       <c r="D25" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E25">
+        <f t="shared" si="0"/>
+        <v>625</v>
+      </c>
+      <c r="F25">
+        <v>0.5</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="1"/>
+        <v>1250</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="2"/>
+        <v>3.0969100130080562</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>3</v>
       </c>
@@ -905,8 +1254,23 @@
       <c r="D26" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E26" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F26">
+        <v>0.5</v>
+      </c>
+      <c r="G26" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H26" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>3</v>
       </c>
@@ -919,8 +1283,23 @@
       <c r="D27" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E27">
+        <f t="shared" si="0"/>
+        <v>525</v>
+      </c>
+      <c r="F27">
+        <v>0.5</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="1"/>
+        <v>1050</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="2"/>
+        <v>3.0211892990699383</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>3</v>
       </c>
@@ -933,8 +1312,23 @@
       <c r="D28" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E28">
+        <f t="shared" si="0"/>
+        <v>375</v>
+      </c>
+      <c r="F28">
+        <v>0.5</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="1"/>
+        <v>750</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="2"/>
+        <v>2.8750612633917001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>3</v>
       </c>
@@ -947,8 +1341,23 @@
       <c r="D29" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E29">
+        <f t="shared" si="0"/>
+        <v>625</v>
+      </c>
+      <c r="F29">
+        <v>0.5</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="1"/>
+        <v>1250</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="2"/>
+        <v>3.0969100130080562</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>3</v>
       </c>
@@ -961,8 +1370,23 @@
       <c r="D30" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E30" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F30">
+        <v>0.5</v>
+      </c>
+      <c r="G30" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H30" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>3</v>
       </c>
@@ -975,8 +1399,23 @@
       <c r="D31" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E31" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F31">
+        <v>0.5</v>
+      </c>
+      <c r="G31" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H31" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>3</v>
       </c>
@@ -989,8 +1428,23 @@
       <c r="D32" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E32">
+        <f t="shared" si="0"/>
+        <v>3625</v>
+      </c>
+      <c r="F32">
+        <v>0.5</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="1"/>
+        <v>7250</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="2"/>
+        <v>3.8603380065709936</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>3</v>
       </c>
@@ -1003,8 +1457,23 @@
       <c r="D33" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E33">
+        <f t="shared" si="0"/>
+        <v>5625</v>
+      </c>
+      <c r="F33">
+        <v>0.5</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="1"/>
+        <v>11250</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="2"/>
+        <v>4.0511525224473814</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>3</v>
       </c>
@@ -1017,8 +1486,23 @@
       <c r="D34" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E34" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F34">
+        <v>0.5</v>
+      </c>
+      <c r="G34" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H34" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>3</v>
       </c>
@@ -1031,8 +1515,23 @@
       <c r="D35" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E35">
+        <f t="shared" si="0"/>
+        <v>2075</v>
+      </c>
+      <c r="F35">
+        <v>0.5</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="1"/>
+        <v>4150</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="2"/>
+        <v>3.6180480967120925</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>3</v>
       </c>
@@ -1045,8 +1544,23 @@
       <c r="D36" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E36">
+        <f t="shared" si="0"/>
+        <v>1125</v>
+      </c>
+      <c r="F36">
+        <v>0.5</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="1"/>
+        <v>2250</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="2"/>
+        <v>3.3521825181113627</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>3</v>
       </c>
@@ -1059,8 +1573,23 @@
       <c r="D37" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E37">
+        <f t="shared" si="0"/>
+        <v>4375</v>
+      </c>
+      <c r="F37">
+        <v>0.5</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="1"/>
+        <v>8750</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="2"/>
+        <v>3.9420080530223132</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>4</v>
       </c>
@@ -1073,8 +1602,23 @@
       <c r="D38" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E38" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F38">
+        <v>0.5</v>
+      </c>
+      <c r="G38" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H38" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>4</v>
       </c>
@@ -1087,8 +1631,23 @@
       <c r="D39" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E39">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="F39">
+        <v>0.5</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="1"/>
+        <v>1800</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="2"/>
+        <v>3.255272505103306</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>4</v>
       </c>
@@ -1101,8 +1660,23 @@
       <c r="D40" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E40">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="F40">
+        <v>0.5</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="2"/>
+        <v>3.1760912590556813</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>4</v>
       </c>
@@ -1115,8 +1689,23 @@
       <c r="D41" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0.5</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H41" t="e">
+        <f t="shared" si="2"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>4</v>
       </c>
@@ -1129,8 +1718,23 @@
       <c r="D42" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E42" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F42">
+        <v>0.5</v>
+      </c>
+      <c r="G42" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H42" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>4</v>
       </c>
@@ -1143,8 +1747,23 @@
       <c r="D43" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E43">
+        <f t="shared" si="0"/>
+        <v>775</v>
+      </c>
+      <c r="F43">
+        <v>0.5</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="1"/>
+        <v>1550</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="2"/>
+        <v>3.1903316981702914</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>4</v>
       </c>
@@ -1157,8 +1776,23 @@
       <c r="D44" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E44">
+        <f t="shared" si="0"/>
+        <v>1125</v>
+      </c>
+      <c r="F44">
+        <v>0.5</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="1"/>
+        <v>2250</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="2"/>
+        <v>3.3521825181113627</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>4</v>
       </c>
@@ -1171,8 +1805,23 @@
       <c r="D45" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E45">
+        <f t="shared" si="0"/>
+        <v>625</v>
+      </c>
+      <c r="F45">
+        <v>0.5</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="1"/>
+        <v>1250</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="2"/>
+        <v>3.0969100130080562</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>4</v>
       </c>
@@ -1185,8 +1834,23 @@
       <c r="D46" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E46" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F46">
+        <v>0.5</v>
+      </c>
+      <c r="G46" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H46" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>4</v>
       </c>
@@ -1199,8 +1863,23 @@
       <c r="D47" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E47">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="F47">
+        <v>0.5</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="1"/>
+        <v>1900</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="2"/>
+        <v>3.2787536009528289</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>4</v>
       </c>
@@ -1213,8 +1892,23 @@
       <c r="D48" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E48">
+        <f t="shared" si="0"/>
+        <v>375</v>
+      </c>
+      <c r="F48">
+        <v>0.5</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="1"/>
+        <v>750</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="2"/>
+        <v>2.8750612633917001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>4</v>
       </c>
@@ -1227,8 +1921,23 @@
       <c r="D49" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E49">
+        <f t="shared" si="0"/>
+        <v>1875</v>
+      </c>
+      <c r="F49">
+        <v>0.5</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="1"/>
+        <v>3750</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="2"/>
+        <v>3.5740312677277188</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>5</v>
       </c>
@@ -1241,8 +1950,23 @@
       <c r="D50" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E50">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="F50">
+        <v>0.5</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>5</v>
       </c>
@@ -1255,8 +1979,23 @@
       <c r="D51" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E51">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="F51">
+        <v>0.5</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="2"/>
+        <v>1.6989700043360187</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>5</v>
       </c>
@@ -1269,8 +2008,23 @@
       <c r="D52" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E52">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0.5</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H52" t="e">
+        <f t="shared" si="2"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>5</v>
       </c>
@@ -1283,8 +2037,23 @@
       <c r="D53" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0.5</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H53" t="e">
+        <f t="shared" si="2"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>5</v>
       </c>
@@ -1297,8 +2066,23 @@
       <c r="D54" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E54">
+        <f t="shared" si="0"/>
+        <v>155</v>
+      </c>
+      <c r="F54">
+        <v>0.5</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="1"/>
+        <v>310</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="2"/>
+        <v>2.4913616938342726</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>5</v>
       </c>
@@ -1311,8 +2095,23 @@
       <c r="D55" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E55">
+        <f t="shared" si="0"/>
+        <v>325</v>
+      </c>
+      <c r="F55">
+        <v>0.5</v>
+      </c>
+      <c r="G55">
+        <f t="shared" si="1"/>
+        <v>650</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="2"/>
+        <v>2.8129133566428557</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>5</v>
       </c>
@@ -1325,8 +2124,23 @@
       <c r="D56" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E56">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="F56">
+        <v>0.5</v>
+      </c>
+      <c r="G56">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>5</v>
       </c>
@@ -1339,8 +2153,23 @@
       <c r="D57" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E57">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0.5</v>
+      </c>
+      <c r="G57">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H57" t="e">
+        <f t="shared" si="2"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>5</v>
       </c>
@@ -1353,8 +2182,23 @@
       <c r="D58" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E58" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F58">
+        <v>0.5</v>
+      </c>
+      <c r="G58" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H58" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>5</v>
       </c>
@@ -1367,8 +2211,23 @@
       <c r="D59" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E59">
+        <f t="shared" si="0"/>
+        <v>1350</v>
+      </c>
+      <c r="F59">
+        <v>0.5</v>
+      </c>
+      <c r="G59">
+        <f t="shared" si="1"/>
+        <v>2700</v>
+      </c>
+      <c r="H59">
+        <f t="shared" si="2"/>
+        <v>3.4313637641589874</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>5</v>
       </c>
@@ -1381,8 +2240,23 @@
       <c r="D60" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E60">
+        <f t="shared" si="0"/>
+        <v>3250</v>
+      </c>
+      <c r="F60">
+        <v>0.5</v>
+      </c>
+      <c r="G60">
+        <f t="shared" si="1"/>
+        <v>6500</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="2"/>
+        <v>3.8129133566428557</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>5</v>
       </c>
@@ -1395,8 +2269,23 @@
       <c r="D61" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E61">
+        <f t="shared" si="0"/>
+        <v>1875</v>
+      </c>
+      <c r="F61">
+        <v>0.5</v>
+      </c>
+      <c r="G61">
+        <f t="shared" si="1"/>
+        <v>3750</v>
+      </c>
+      <c r="H61">
+        <f t="shared" si="2"/>
+        <v>3.5740312677277188</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>6</v>
       </c>
@@ -1409,8 +2298,23 @@
       <c r="D62" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E62" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F62">
+        <v>0.5</v>
+      </c>
+      <c r="G62" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H62" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>6</v>
       </c>
@@ -1423,8 +2327,23 @@
       <c r="D63" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E63">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="F63">
+        <v>0.5</v>
+      </c>
+      <c r="G63">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="H63">
+        <f t="shared" si="2"/>
+        <v>3.3979400086720375</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>6</v>
       </c>
@@ -1437,8 +2356,23 @@
       <c r="D64" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E64">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="F64">
+        <v>0.5</v>
+      </c>
+      <c r="G64">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="2"/>
+        <v>3.4771212547196626</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>6</v>
       </c>
@@ -1451,8 +2385,23 @@
       <c r="D65" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E65">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="F65">
+        <v>0.5</v>
+      </c>
+      <c r="G65">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="2"/>
+        <v>3.3979400086720375</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>6</v>
       </c>
@@ -1465,8 +2414,23 @@
       <c r="D66" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E66" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F66">
+        <v>0.5</v>
+      </c>
+      <c r="G66" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H66" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>6</v>
       </c>
@@ -1479,8 +2443,23 @@
       <c r="D67" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E67" t="e">
+        <f t="shared" ref="E67:E121" si="3">D67*(5^C67)*10*0.5</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F67">
+        <v>0.5</v>
+      </c>
+      <c r="G67" t="e">
+        <f t="shared" ref="G67:G121" si="4">E67/F67</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H67" t="e">
+        <f t="shared" ref="H67:H121" si="5">LOG(G67)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>6</v>
       </c>
@@ -1493,8 +2472,23 @@
       <c r="D68" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E68">
+        <f t="shared" si="3"/>
+        <v>2750</v>
+      </c>
+      <c r="F68">
+        <v>0.5</v>
+      </c>
+      <c r="G68">
+        <f t="shared" si="4"/>
+        <v>5500</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="5"/>
+        <v>3.7403626894942437</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>6</v>
       </c>
@@ -1507,8 +2501,23 @@
       <c r="D69" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E69">
+        <f t="shared" si="3"/>
+        <v>3125</v>
+      </c>
+      <c r="F69">
+        <v>0.5</v>
+      </c>
+      <c r="G69">
+        <f t="shared" si="4"/>
+        <v>6250</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="5"/>
+        <v>3.7958800173440754</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>6</v>
       </c>
@@ -1521,8 +2530,23 @@
       <c r="D70" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E70" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F70">
+        <v>0.5</v>
+      </c>
+      <c r="G70" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H70" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>6</v>
       </c>
@@ -1535,8 +2559,23 @@
       <c r="D71" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E71" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F71">
+        <v>0.5</v>
+      </c>
+      <c r="G71" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H71" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>6</v>
       </c>
@@ -1549,8 +2588,23 @@
       <c r="D72" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E72" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F72">
+        <v>0.5</v>
+      </c>
+      <c r="G72" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H72" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>6</v>
       </c>
@@ -1563,8 +2617,23 @@
       <c r="D73" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E73">
+        <f t="shared" si="3"/>
+        <v>110625</v>
+      </c>
+      <c r="F73">
+        <v>0.5</v>
+      </c>
+      <c r="G73">
+        <f t="shared" si="4"/>
+        <v>221250</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="5"/>
+        <v>5.3448832793698626</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>7</v>
       </c>
@@ -1577,8 +2646,23 @@
       <c r="D74" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E74">
+        <f t="shared" si="3"/>
+        <v>160</v>
+      </c>
+      <c r="F74">
+        <v>0.5</v>
+      </c>
+      <c r="G74">
+        <f t="shared" si="4"/>
+        <v>320</v>
+      </c>
+      <c r="H74">
+        <f t="shared" si="5"/>
+        <v>2.5051499783199058</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>7</v>
       </c>
@@ -1591,8 +2675,23 @@
       <c r="D75" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E75">
+        <f t="shared" si="3"/>
+        <v>650</v>
+      </c>
+      <c r="F75">
+        <v>0.5</v>
+      </c>
+      <c r="G75">
+        <f t="shared" si="4"/>
+        <v>1300</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="5"/>
+        <v>3.1139433523068369</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>7</v>
       </c>
@@ -1605,8 +2704,23 @@
       <c r="D76" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E76">
+        <f t="shared" si="3"/>
+        <v>500</v>
+      </c>
+      <c r="F76">
+        <v>0.5</v>
+      </c>
+      <c r="G76">
+        <f t="shared" si="4"/>
+        <v>1000</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>7</v>
       </c>
@@ -1619,8 +2733,23 @@
       <c r="D77" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E77">
+        <f t="shared" si="3"/>
+        <v>625</v>
+      </c>
+      <c r="F77">
+        <v>0.5</v>
+      </c>
+      <c r="G77">
+        <f t="shared" si="4"/>
+        <v>1250</v>
+      </c>
+      <c r="H77">
+        <f t="shared" si="5"/>
+        <v>3.0969100130080562</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>7</v>
       </c>
@@ -1633,8 +2762,23 @@
       <c r="D78" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E78">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="F78">
+        <v>0.5</v>
+      </c>
+      <c r="G78">
+        <f t="shared" si="4"/>
+        <v>400</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="5"/>
+        <v>2.6020599913279625</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>7</v>
       </c>
@@ -1647,8 +2791,23 @@
       <c r="D79" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E79">
+        <f t="shared" si="3"/>
+        <v>400</v>
+      </c>
+      <c r="F79">
+        <v>0.5</v>
+      </c>
+      <c r="G79">
+        <f t="shared" si="4"/>
+        <v>800</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="5"/>
+        <v>2.9030899869919438</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>7</v>
       </c>
@@ -1661,8 +2820,23 @@
       <c r="D80" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E80">
+        <f t="shared" si="3"/>
+        <v>625</v>
+      </c>
+      <c r="F80">
+        <v>0.5</v>
+      </c>
+      <c r="G80">
+        <f t="shared" si="4"/>
+        <v>1250</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="5"/>
+        <v>3.0969100130080562</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>7</v>
       </c>
@@ -1675,8 +2849,23 @@
       <c r="D81" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E81">
+        <f t="shared" si="3"/>
+        <v>625</v>
+      </c>
+      <c r="F81">
+        <v>0.5</v>
+      </c>
+      <c r="G81">
+        <f t="shared" si="4"/>
+        <v>1250</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="5"/>
+        <v>3.0969100130080562</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>7</v>
       </c>
@@ -1689,8 +2878,23 @@
       <c r="D82" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E82">
+        <f t="shared" si="3"/>
+        <v>340</v>
+      </c>
+      <c r="F82">
+        <v>0.5</v>
+      </c>
+      <c r="G82">
+        <f t="shared" si="4"/>
+        <v>680</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="5"/>
+        <v>2.8325089127062362</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>7</v>
       </c>
@@ -1703,8 +2907,23 @@
       <c r="D83" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E83">
+        <f t="shared" si="3"/>
+        <v>550</v>
+      </c>
+      <c r="F83">
+        <v>0.5</v>
+      </c>
+      <c r="G83">
+        <f t="shared" si="4"/>
+        <v>1100</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="5"/>
+        <v>3.0413926851582249</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>7</v>
       </c>
@@ -1717,8 +2936,23 @@
       <c r="D84" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E84">
+        <f t="shared" si="3"/>
+        <v>125</v>
+      </c>
+      <c r="F84">
+        <v>0.5</v>
+      </c>
+      <c r="G84">
+        <f t="shared" si="4"/>
+        <v>250</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="5"/>
+        <v>2.3979400086720375</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>7</v>
       </c>
@@ -1731,8 +2965,23 @@
       <c r="D85" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E85">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0.5</v>
+      </c>
+      <c r="G85">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H85" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>8</v>
       </c>
@@ -1745,8 +2994,23 @@
       <c r="D86" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E86" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F86">
+        <v>0.5</v>
+      </c>
+      <c r="G86" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H86" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>8</v>
       </c>
@@ -1759,8 +3023,23 @@
       <c r="D87" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E87">
+        <f t="shared" si="3"/>
+        <v>600</v>
+      </c>
+      <c r="F87">
+        <v>0.5</v>
+      </c>
+      <c r="G87">
+        <f t="shared" si="4"/>
+        <v>1200</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="5"/>
+        <v>3.0791812460476247</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>8</v>
       </c>
@@ -1773,8 +3052,23 @@
       <c r="D88" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E88">
+        <f t="shared" si="3"/>
+        <v>875</v>
+      </c>
+      <c r="F88">
+        <v>0.5</v>
+      </c>
+      <c r="G88">
+        <f t="shared" si="4"/>
+        <v>1750</v>
+      </c>
+      <c r="H88">
+        <f t="shared" si="5"/>
+        <v>3.2430380486862944</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>8</v>
       </c>
@@ -1787,8 +3081,23 @@
       <c r="D89" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E89" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F89">
+        <v>0.5</v>
+      </c>
+      <c r="G89" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H89" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>8</v>
       </c>
@@ -1801,8 +3110,23 @@
       <c r="D90" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E90">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="F90">
+        <v>0.5</v>
+      </c>
+      <c r="G90">
+        <f t="shared" si="4"/>
+        <v>200</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="5"/>
+        <v>2.3010299956639813</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>8</v>
       </c>
@@ -1815,8 +3139,23 @@
       <c r="D91" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E91">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="F91">
+        <v>0.5</v>
+      </c>
+      <c r="G91">
+        <f t="shared" si="4"/>
+        <v>400</v>
+      </c>
+      <c r="H91">
+        <f t="shared" si="5"/>
+        <v>2.6020599913279625</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>8</v>
       </c>
@@ -1829,8 +3168,23 @@
       <c r="D92" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E92">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0.5</v>
+      </c>
+      <c r="G92">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H92" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>8</v>
       </c>
@@ -1843,8 +3197,23 @@
       <c r="D93" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E93">
+        <f t="shared" si="3"/>
+        <v>625</v>
+      </c>
+      <c r="F93">
+        <v>0.5</v>
+      </c>
+      <c r="G93">
+        <f t="shared" si="4"/>
+        <v>1250</v>
+      </c>
+      <c r="H93">
+        <f t="shared" si="5"/>
+        <v>3.0969100130080562</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>8</v>
       </c>
@@ -1857,8 +3226,23 @@
       <c r="D94" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E94" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F94">
+        <v>0.5</v>
+      </c>
+      <c r="G94" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H94" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>8</v>
       </c>
@@ -1871,8 +3255,23 @@
       <c r="D95" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E95">
+        <f t="shared" si="3"/>
+        <v>1725</v>
+      </c>
+      <c r="F95">
+        <v>0.5</v>
+      </c>
+      <c r="G95">
+        <f t="shared" si="4"/>
+        <v>3450</v>
+      </c>
+      <c r="H95">
+        <f t="shared" si="5"/>
+        <v>3.537819095073274</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>8</v>
       </c>
@@ -1885,8 +3284,23 @@
       <c r="D96" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E96">
+        <f t="shared" si="3"/>
+        <v>1750</v>
+      </c>
+      <c r="F96">
+        <v>0.5</v>
+      </c>
+      <c r="G96">
+        <f t="shared" si="4"/>
+        <v>3500</v>
+      </c>
+      <c r="H96">
+        <f t="shared" si="5"/>
+        <v>3.5440680443502757</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>8</v>
       </c>
@@ -1899,8 +3313,23 @@
       <c r="D97" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E97">
+        <f t="shared" si="3"/>
+        <v>2500</v>
+      </c>
+      <c r="F97">
+        <v>0.5</v>
+      </c>
+      <c r="G97">
+        <f t="shared" si="4"/>
+        <v>5000</v>
+      </c>
+      <c r="H97">
+        <f t="shared" si="5"/>
+        <v>3.6989700043360187</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>9</v>
       </c>
@@ -1913,8 +3342,23 @@
       <c r="D98" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E98">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="F98">
+        <v>0.5</v>
+      </c>
+      <c r="G98">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="H98">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>9</v>
       </c>
@@ -1927,8 +3371,23 @@
       <c r="D99" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E99">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="F99">
+        <v>0.5</v>
+      </c>
+      <c r="G99">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="H99">
+        <f t="shared" si="5"/>
+        <v>1.6989700043360187</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>9</v>
       </c>
@@ -1941,8 +3400,23 @@
       <c r="D100" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E100">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0.5</v>
+      </c>
+      <c r="G100">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H100" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>9</v>
       </c>
@@ -1955,8 +3429,23 @@
       <c r="D101" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E101">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>0.5</v>
+      </c>
+      <c r="G101">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H101" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>9</v>
       </c>
@@ -1969,8 +3458,23 @@
       <c r="D102" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E102">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="F102">
+        <v>0.5</v>
+      </c>
+      <c r="G102">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="H102">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>9</v>
       </c>
@@ -1983,8 +3487,23 @@
       <c r="D103" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0.5</v>
+      </c>
+      <c r="G103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H103" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>9</v>
       </c>
@@ -1997,8 +3516,23 @@
       <c r="D104" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E104">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0.5</v>
+      </c>
+      <c r="G104">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H104" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>9</v>
       </c>
@@ -2011,8 +3545,23 @@
       <c r="D105" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E105">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0.5</v>
+      </c>
+      <c r="G105">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H105" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>9</v>
       </c>
@@ -2025,8 +3574,23 @@
       <c r="D106" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E106">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="F106">
+        <v>0.5</v>
+      </c>
+      <c r="G106">
+        <f t="shared" si="4"/>
+        <v>400</v>
+      </c>
+      <c r="H106">
+        <f t="shared" si="5"/>
+        <v>2.6020599913279625</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>9</v>
       </c>
@@ -2039,8 +3603,23 @@
       <c r="D107" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E107">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="F107">
+        <v>0.5</v>
+      </c>
+      <c r="G107">
+        <f t="shared" si="4"/>
+        <v>400</v>
+      </c>
+      <c r="H107">
+        <f t="shared" si="5"/>
+        <v>2.6020599913279625</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>9</v>
       </c>
@@ -2053,8 +3632,23 @@
       <c r="D108" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E108">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>0.5</v>
+      </c>
+      <c r="G108">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H108" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>9</v>
       </c>
@@ -2067,8 +3661,23 @@
       <c r="D109" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E109">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>0.5</v>
+      </c>
+      <c r="G109">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H109" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>10</v>
       </c>
@@ -2081,8 +3690,23 @@
       <c r="D110" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E110">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>0.5</v>
+      </c>
+      <c r="G110">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H110" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>10</v>
       </c>
@@ -2095,8 +3719,23 @@
       <c r="D111" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E111">
+        <f t="shared" si="3"/>
+        <v>700</v>
+      </c>
+      <c r="F111">
+        <v>0.5</v>
+      </c>
+      <c r="G111">
+        <f t="shared" si="4"/>
+        <v>1400</v>
+      </c>
+      <c r="H111">
+        <f t="shared" si="5"/>
+        <v>3.1461280356782382</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>10</v>
       </c>
@@ -2109,8 +3748,23 @@
       <c r="D112" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E112">
+        <f t="shared" si="3"/>
+        <v>625</v>
+      </c>
+      <c r="F112">
+        <v>0.5</v>
+      </c>
+      <c r="G112">
+        <f t="shared" si="4"/>
+        <v>1250</v>
+      </c>
+      <c r="H112">
+        <f t="shared" si="5"/>
+        <v>3.0969100130080562</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>10</v>
       </c>
@@ -2123,8 +3777,23 @@
       <c r="D113" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E113">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0.5</v>
+      </c>
+      <c r="G113">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H113" t="e">
+        <f t="shared" si="5"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>10</v>
       </c>
@@ -2137,8 +3806,23 @@
       <c r="D114" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E114" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F114">
+        <v>0.5</v>
+      </c>
+      <c r="G114" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H114" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>10</v>
       </c>
@@ -2151,8 +3835,23 @@
       <c r="D115" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E115">
+        <f t="shared" si="3"/>
+        <v>1725</v>
+      </c>
+      <c r="F115">
+        <v>0.5</v>
+      </c>
+      <c r="G115">
+        <f t="shared" si="4"/>
+        <v>3450</v>
+      </c>
+      <c r="H115">
+        <f t="shared" si="5"/>
+        <v>3.537819095073274</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>10</v>
       </c>
@@ -2165,8 +3864,23 @@
       <c r="D116" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E116">
+        <f t="shared" si="3"/>
+        <v>1750</v>
+      </c>
+      <c r="F116">
+        <v>0.5</v>
+      </c>
+      <c r="G116">
+        <f t="shared" si="4"/>
+        <v>3500</v>
+      </c>
+      <c r="H116">
+        <f t="shared" si="5"/>
+        <v>3.5440680443502757</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>10</v>
       </c>
@@ -2179,8 +3893,23 @@
       <c r="D117" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E117">
+        <f t="shared" si="3"/>
+        <v>1875</v>
+      </c>
+      <c r="F117">
+        <v>0.5</v>
+      </c>
+      <c r="G117">
+        <f t="shared" si="4"/>
+        <v>3750</v>
+      </c>
+      <c r="H117">
+        <f t="shared" si="5"/>
+        <v>3.5740312677277188</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>10</v>
       </c>
@@ -2193,8 +3922,23 @@
       <c r="D118" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E118" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F118">
+        <v>0.5</v>
+      </c>
+      <c r="G118" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H118" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>10</v>
       </c>
@@ -2207,8 +3951,23 @@
       <c r="D119" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E119" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F119">
+        <v>0.5</v>
+      </c>
+      <c r="G119" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H119" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>10</v>
       </c>
@@ -2221,8 +3980,23 @@
       <c r="D120" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E120">
+        <f t="shared" si="3"/>
+        <v>4250</v>
+      </c>
+      <c r="F120">
+        <v>0.5</v>
+      </c>
+      <c r="G120">
+        <f t="shared" si="4"/>
+        <v>8500</v>
+      </c>
+      <c r="H120">
+        <f t="shared" si="5"/>
+        <v>3.9294189257142929</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>10</v>
       </c>
@@ -2234,6 +4008,21 @@
       </c>
       <c r="D121" t="s">
         <v>10</v>
+      </c>
+      <c r="E121">
+        <f t="shared" si="3"/>
+        <v>3125</v>
+      </c>
+      <c r="F121">
+        <v>0.5</v>
+      </c>
+      <c r="G121">
+        <f t="shared" si="4"/>
+        <v>6250</v>
+      </c>
+      <c r="H121">
+        <f t="shared" si="5"/>
+        <v>3.7958800173440754</v>
       </c>
     </row>
   </sheetData>
